--- a/outputs/per-fund/vc-investments-semantic-ventures.xlsx
+++ b/outputs/per-fund/vc-investments-semantic-ventures.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Semantic Ventures. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Semantic Ventures. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -5765,11 +5765,11 @@
         <v>0</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" s="5" t="inlineStr">
         <is>
-          <t>semantic-ventures</t>
+          <t>fenbushi-capital, semantic-ventures</t>
         </is>
       </c>
       <c r="M2" s="7" t="inlineStr">
@@ -5828,11 +5828,11 @@
         <v>2</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures</t>
+          <t>coinbase-ventures, founders-fund, multicoin-capital, pantera, paradigm, semantic-ventures, sequoia-capital</t>
         </is>
       </c>
       <c r="M3" s="7" t="inlineStr">
@@ -6013,11 +6013,11 @@
         <v>0</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>lemniscap, semantic-ventures</t>
+          <t>galaxy-digital, lemniscap, semantic-ventures</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -6076,11 +6076,11 @@
         <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>semantic-ventures</t>
+          <t>alliance-dao, semantic-ventures</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -6139,11 +6139,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, lemniscap, semantic-ventures</t>
+          <t>coinbase-ventures, coinfund, electric-capital, framework-ventures, hypersphere, lemniscap, semantic-ventures</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -6202,11 +6202,11 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, multicoin-capital, semantic-ventures</t>
+          <t>alliance-dao, delphi-ventures, multicoin-capital, semantic-ventures</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -6265,11 +6265,11 @@
         <v>1</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>semantic-ventures</t>
+          <t>galaxy-digital, semantic-ventures</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -6454,11 +6454,11 @@
         <v>2</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, semantic-ventures</t>
+          <t>1kx, coinbase-ventures, semantic-ventures</t>
         </is>
       </c>
       <c r="M13" s="7" t="inlineStr">
@@ -6517,11 +6517,11 @@
         <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, semantic-ventures</t>
+          <t>coinbase-ventures, hashed, semantic-ventures</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -6643,11 +6643,11 @@
         <v>2</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, semantic-ventures</t>
+          <t>a16z-crypto, coinbase-ventures, gsr, mechanism-capital, semantic-ventures</t>
         </is>
       </c>
       <c r="M16" s="7" t="inlineStr">
@@ -6889,11 +6889,11 @@
         <v>2</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, semantic-ventures</t>
+          <t>coinfund, delphi-ventures, longhash-ventures, semantic-ventures, yzi-labs</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -7263,11 +7263,11 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, pantera, robot-ventures, semantic-ventures</t>
+          <t>a16z-crypto, coinbase-ventures, fenbushi-capital, hack-vc, iosg-ventures, mirana-ventures, pantera, robot-ventures, semantic-ventures</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -7391,11 +7391,11 @@
         <v>1</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures</t>
+          <t>delphi-ventures, figment-capital, robot-ventures, semantic-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -7454,11 +7454,11 @@
         <v>1</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>semantic-ventures</t>
+          <t>hashed, semantic-ventures</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -7643,11 +7643,11 @@
         <v>1</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>semantic-ventures</t>
+          <t>borderless-capital, semantic-ventures</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -9258,19 +9258,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
